--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FC BARCELONA.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FC BARCELONA.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>40.4983</v>
+        <v>50.8406</v>
       </c>
       <c r="E2" t="n">
-        <v>22.3149</v>
+        <v>30.2763</v>
       </c>
       <c r="F2" t="n">
-        <v>18.1835</v>
+        <v>20.5642</v>
       </c>
       <c r="G2" t="n">
         <v>49.9476</v>
@@ -610,13 +610,13 @@
         <v>64.9469</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.8609</v>
+        <v>3.481</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.448</v>
+        <v>0.5132999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5871000000000003</v>
+        <v>2.9681</v>
       </c>
       <c r="V2" t="n">
         <v>-9.082600000000001</v>
@@ -643,13 +643,13 @@
         <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1498</v>
+        <v>22.2471</v>
       </c>
       <c r="E3" t="n">
-        <v>32.2376</v>
+        <v>26.1507</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.0874</v>
+        <v>-3.9035</v>
       </c>
       <c r="G3" t="n">
         <v>19.2675</v>
@@ -688,13 +688,13 @@
         <v>56.3646</v>
       </c>
       <c r="S3" t="n">
-        <v>16.0908</v>
+        <v>10.1881</v>
       </c>
       <c r="T3" t="n">
-        <v>11.4859</v>
+        <v>5.3989</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6048</v>
+        <v>4.7893</v>
       </c>
       <c r="V3" t="n">
         <v>3.9256</v>
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>20.9008</v>
+        <v>16.472</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3656</v>
+        <v>13.4614</v>
       </c>
       <c r="F4" t="n">
-        <v>3.534800000000001</v>
+        <v>3.0106</v>
       </c>
       <c r="G4" t="n">
         <v>4.683199999999999</v>
@@ -766,13 +766,13 @@
         <v>7.8866</v>
       </c>
       <c r="S4" t="n">
-        <v>11.1483</v>
+        <v>6.719399999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>7.621</v>
+        <v>3.7169</v>
       </c>
       <c r="U4" t="n">
-        <v>3.5272</v>
+        <v>3.0031</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9615000000000002</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>14.9984</v>
+        <v>11.313</v>
       </c>
       <c r="E5" t="n">
-        <v>13.5761</v>
+        <v>8.0458</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4231</v>
+        <v>3.2673</v>
       </c>
       <c r="G5" t="n">
-        <v>-17.4244</v>
+        <v>-6.559000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.7128</v>
+        <v>-28.1887</v>
       </c>
       <c r="I5" t="n">
-        <v>-14.7115</v>
+        <v>21.6293</v>
       </c>
       <c r="J5" t="n">
-        <v>12.8275</v>
+        <v>38.0456</v>
       </c>
       <c r="K5" t="n">
-        <v>15.6911</v>
+        <v>1.580999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.863299999999999</v>
+        <v>36.4647</v>
       </c>
       <c r="M5" t="n">
-        <v>-30.2517</v>
+        <v>-44.6046</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.4038</v>
+        <v>-29.7696</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.8485</v>
+        <v>-14.835</v>
       </c>
       <c r="P5" t="n">
-        <v>28.7625</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-26.6751</v>
+        <v>-72.833</v>
       </c>
       <c r="R5" t="n">
-        <v>55.4369</v>
+        <v>71.20950000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>15.8008</v>
+        <v>-10.384</v>
       </c>
       <c r="T5" t="n">
-        <v>12.7441</v>
+        <v>-5.3985</v>
       </c>
       <c r="U5" t="n">
-        <v>3.0569</v>
+        <v>-4.985300000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-12.14</v>
+        <v>29.8798</v>
       </c>
       <c r="W5" t="n">
-        <v>14.6787</v>
+        <v>48.2316</v>
       </c>
       <c r="X5" t="n">
-        <v>-26.8187</v>
+        <v>-18.3518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>12.495</v>
+        <v>7.291400000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>12.8773</v>
+        <v>5.570499999999998</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3824999999999993</v>
+        <v>1.721099999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.245500000000001</v>
+        <v>-17.4244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3658000000000001</v>
+        <v>-2.7128</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.6115</v>
+        <v>-14.7115</v>
       </c>
       <c r="J6" t="n">
-        <v>13.2074</v>
+        <v>12.8275</v>
       </c>
       <c r="K6" t="n">
-        <v>9.392300000000001</v>
+        <v>15.6911</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8157</v>
+        <v>-2.863299999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.4532</v>
+        <v>-30.2517</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.026400000000001</v>
+        <v>-18.4038</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.426699999999999</v>
+        <v>-11.8485</v>
       </c>
       <c r="P6" t="n">
-        <v>15.7733</v>
+        <v>28.7625</v>
       </c>
       <c r="Q6" t="n">
-        <v>-12.2938</v>
+        <v>-26.6751</v>
       </c>
       <c r="R6" t="n">
-        <v>28.0667</v>
+        <v>55.4369</v>
       </c>
       <c r="S6" t="n">
-        <v>9.811299999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="T6" t="n">
-        <v>8.2103</v>
+        <v>4.738599999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6011</v>
+        <v>3.3549</v>
       </c>
       <c r="V6" t="n">
-        <v>-8.8438</v>
+        <v>-12.14</v>
       </c>
       <c r="W6" t="n">
-        <v>3.7527</v>
+        <v>14.6787</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.5965</v>
+        <v>-26.8187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>8.2288</v>
+        <v>5.2958</v>
       </c>
       <c r="E7" t="n">
-        <v>5.223800000000001</v>
+        <v>7.018800000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>3.005199999999999</v>
+        <v>-1.7228</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.912700000000001</v>
+        <v>-4.245500000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.9022</v>
+        <v>0.3658000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>9.9895</v>
+        <v>-4.6115</v>
       </c>
       <c r="J7" t="n">
-        <v>26.3425</v>
+        <v>13.2074</v>
       </c>
       <c r="K7" t="n">
-        <v>9.9054</v>
+        <v>9.392300000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>16.437</v>
+        <v>3.8157</v>
       </c>
       <c r="M7" t="n">
-        <v>-28.2552</v>
+        <v>-17.4532</v>
       </c>
       <c r="N7" t="n">
-        <v>-21.8077</v>
+        <v>-9.026400000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.4475</v>
+        <v>-8.426699999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>20.4119</v>
+        <v>15.7733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-39.2005</v>
+        <v>-12.2938</v>
       </c>
       <c r="R7" t="n">
-        <v>59.612</v>
+        <v>28.0667</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8388</v>
+        <v>2.6125</v>
       </c>
       <c r="T7" t="n">
-        <v>4.8688</v>
+        <v>2.3519</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.0304</v>
+        <v>0.2605999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-12.1089</v>
+        <v>-8.8438</v>
       </c>
       <c r="W7" t="n">
-        <v>13.2122</v>
+        <v>3.7527</v>
       </c>
       <c r="X7" t="n">
-        <v>-25.3211</v>
+        <v>-12.5965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.033400000000001</v>
+        <v>4.3738</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8826999999999995</v>
+        <v>-0.2923999999999995</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1510999999999999</v>
+        <v>4.666499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.9726</v>
+        <v>-1.912700000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.19</v>
+        <v>-11.9022</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.7827</v>
+        <v>9.9895</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4206</v>
+        <v>26.3425</v>
       </c>
       <c r="K8" t="n">
-        <v>6.029299999999999</v>
+        <v>9.9054</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6086</v>
+        <v>16.437</v>
       </c>
       <c r="M8" t="n">
-        <v>-20.3932</v>
+        <v>-28.2552</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.2188</v>
+        <v>-21.8077</v>
       </c>
       <c r="O8" t="n">
-        <v>-13.174</v>
+        <v>-6.4475</v>
       </c>
       <c r="P8" t="n">
-        <v>26.6748</v>
+        <v>20.4119</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.8301</v>
+        <v>-39.2005</v>
       </c>
       <c r="R8" t="n">
-        <v>38.5044</v>
+        <v>59.612</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7271000000000002</v>
+        <v>-2.0164</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2069</v>
+        <v>-0.6474</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.4799</v>
+        <v>-1.3684</v>
       </c>
       <c r="V8" t="n">
-        <v>-11.4621</v>
+        <v>-12.1089</v>
       </c>
       <c r="W8" t="n">
-        <v>4.319900000000001</v>
+        <v>13.2122</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.782</v>
+        <v>-25.3211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2718</v>
+        <v>3.8535</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9357</v>
+        <v>6.1084</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3361</v>
+        <v>-2.255699999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1224</v>
+        <v>5.529700000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1224</v>
+        <v>1.089</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.440700000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7863</v>
+        <v>31.9167</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7863</v>
+        <v>17.3936</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>14.5231</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3361</v>
+        <v>-26.3869</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3361</v>
+        <v>-16.3045</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-10.0824</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.4795</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-39.2001</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>42.6797</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1494</v>
+        <v>1.2282</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>0.6354</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.5927999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-6.3847</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>12.7557</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-19.1404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NUNEZ</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3369</v>
+        <v>2.807800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5514</v>
+        <v>-1.1343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2145</v>
+        <v>3.942</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1253</v>
+        <v>-16.9726</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3193</v>
+        <v>-1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1941</v>
+        <v>-15.7827</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2502</v>
+        <v>3.4206</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.287</v>
+        <v>6.029299999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>-2.6086</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1249</v>
+        <v>-20.3932</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0323</v>
+        <v>-7.2188</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>-13.174</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3917</v>
+        <v>26.6748</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-11.8301</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>38.5044</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1801</v>
+        <v>4.5682</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0905</v>
+        <v>2.955</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0896</v>
+        <v>1.6136</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-11.4621</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4.319900000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-15.782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8523</v>
+        <v>0.3925000000000013</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5136</v>
+        <v>-4.852299999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3388</v>
+        <v>5.2451</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5682000000000005</v>
+        <v>-12.9753</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4418</v>
+        <v>-11.2234</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8736000000000002</v>
+        <v>-1.7518</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6737</v>
+        <v>26.2353</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7905</v>
+        <v>13.2819</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8833</v>
+        <v>12.9533</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.242</v>
+        <v>-39.2107</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2322</v>
+        <v>-24.5053</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.00979999999999992</v>
+        <v>-14.7053</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0877</v>
+        <v>-6.2626</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.6392</v>
+        <v>-61.9314</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5515</v>
+        <v>55.669</v>
       </c>
       <c r="S11" t="n">
-        <v>1.484</v>
+        <v>3.0288</v>
       </c>
       <c r="T11" t="n">
-        <v>1.31</v>
+        <v>0.2096999999999997</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1739</v>
+        <v>2.8192</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6805</v>
+        <v>16.6015</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>30.6333</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8223</v>
+        <v>-14.0319</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.218599999999998</v>
+        <v>-1.2718</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.0499</v>
+        <v>-0.9357</v>
       </c>
       <c r="F12" t="n">
-        <v>6.831600000000001</v>
+        <v>-0.3361</v>
       </c>
       <c r="G12" t="n">
-        <v>-12.9753</v>
+        <v>-1.1224</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.2234</v>
+        <v>-1.1224</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7518</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>26.2353</v>
+        <v>-0.7863</v>
       </c>
       <c r="K12" t="n">
-        <v>13.2819</v>
+        <v>-0.7863</v>
       </c>
       <c r="L12" t="n">
-        <v>12.9533</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-39.2107</v>
+        <v>-0.3361</v>
       </c>
       <c r="N12" t="n">
-        <v>-24.5053</v>
+        <v>-0.3361</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.7053</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.2626</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-61.9314</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>55.669</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5818</v>
+        <v>-0.1494</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.9876</v>
+        <v>-0.1494</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4054</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>16.6015</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>30.6333</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.0319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. NUNEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.791700000000001</v>
+        <v>-2.2024</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7859</v>
+        <v>-2.5514</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.5783</v>
+        <v>0.349</v>
       </c>
       <c r="G13" t="n">
-        <v>-27.3569</v>
+        <v>-1.1253</v>
       </c>
       <c r="H13" t="n">
-        <v>-17.2306</v>
+        <v>-1.3193</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.1268</v>
+        <v>0.1941</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4476000000000003</v>
+        <v>-1.2502</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.959</v>
+        <v>-1.287</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4066</v>
+        <v>0.0368</v>
       </c>
       <c r="M13" t="n">
-        <v>-27.8047</v>
+        <v>0.1249</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.2715</v>
+        <v>-0.0323</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.5333</v>
+        <v>0.1573</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.581999999999999</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-44.5351</v>
+        <v>-1.3917</v>
       </c>
       <c r="R13" t="n">
-        <v>35.9532</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>33.8168</v>
+        <v>0.3145</v>
       </c>
       <c r="T13" t="n">
-        <v>23.25</v>
+        <v>0.0905</v>
       </c>
       <c r="U13" t="n">
-        <v>10.5665</v>
+        <v>0.224</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6695</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>22.6229</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-27.2926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.2549</v>
+        <v>-4.7288</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.5022</v>
+        <v>-2.4572</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.752600000000001</v>
+        <v>-2.2716</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.559000000000001</v>
+        <v>-0.5682000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-28.1887</v>
+        <v>-1.4418</v>
       </c>
       <c r="I14" t="n">
-        <v>21.6293</v>
+        <v>0.8736000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>38.0456</v>
+        <v>1.6737</v>
       </c>
       <c r="K14" t="n">
-        <v>1.580999999999999</v>
+        <v>0.7905</v>
       </c>
       <c r="L14" t="n">
-        <v>36.4647</v>
+        <v>0.8833</v>
       </c>
       <c r="M14" t="n">
-        <v>-44.6046</v>
+        <v>-2.242</v>
       </c>
       <c r="N14" t="n">
-        <v>-29.7696</v>
+        <v>-2.2322</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.835</v>
+        <v>-0.00979999999999992</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.6237</v>
+        <v>-2.0877</v>
       </c>
       <c r="Q14" t="n">
-        <v>-72.833</v>
+        <v>-4.6392</v>
       </c>
       <c r="R14" t="n">
-        <v>71.20950000000001</v>
+        <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-36.9521</v>
+        <v>0.6075</v>
       </c>
       <c r="T14" t="n">
-        <v>-21.9469</v>
+        <v>0.3663</v>
       </c>
       <c r="U14" t="n">
-        <v>-15.0053</v>
+        <v>0.2412</v>
       </c>
       <c r="V14" t="n">
-        <v>29.8798</v>
+        <v>-2.6805</v>
       </c>
       <c r="W14" t="n">
-        <v>48.2316</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.3518</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.4715</v>
+        <v>-17.4249</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.383599999999999</v>
+        <v>-5.534300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.088</v>
+        <v>-11.8904</v>
       </c>
       <c r="G15" t="n">
-        <v>5.529700000000001</v>
+        <v>10.991</v>
       </c>
       <c r="H15" t="n">
-        <v>1.089</v>
+        <v>9.7348</v>
       </c>
       <c r="I15" t="n">
-        <v>4.440700000000001</v>
+        <v>1.2558</v>
       </c>
       <c r="J15" t="n">
-        <v>31.9167</v>
+        <v>28.9323</v>
       </c>
       <c r="K15" t="n">
-        <v>17.3936</v>
+        <v>17.4792</v>
       </c>
       <c r="L15" t="n">
-        <v>14.5231</v>
+        <v>11.4532</v>
       </c>
       <c r="M15" t="n">
-        <v>-26.3869</v>
+        <v>-17.9414</v>
       </c>
       <c r="N15" t="n">
-        <v>-16.3045</v>
+        <v>-7.7443</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.0824</v>
+        <v>-10.1971</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4795</v>
+        <v>-20.8757</v>
       </c>
       <c r="Q15" t="n">
-        <v>-39.2001</v>
+        <v>-43.8388</v>
       </c>
       <c r="R15" t="n">
-        <v>42.6797</v>
+        <v>22.9636</v>
       </c>
       <c r="S15" t="n">
-        <v>-18.0959</v>
+        <v>-3.362</v>
       </c>
       <c r="T15" t="n">
-        <v>-13.8569</v>
+        <v>-1.0976</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.2396</v>
+        <v>-2.2646</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.3847</v>
+        <v>-4.1781</v>
       </c>
       <c r="W15" t="n">
-        <v>12.7557</v>
+        <v>10.4695</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.1404</v>
+        <v>-14.6476</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>-23.2102</v>
+        <v>-18.4573</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.4152</v>
+        <v>-15.2663</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.7949</v>
+        <v>-3.1911</v>
       </c>
       <c r="G16" t="n">
         <v>-4.2263</v>
@@ -1702,13 +1702,13 @@
         <v>17.1648</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.6152</v>
+        <v>1.1376</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.8027</v>
+        <v>-0.6536000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1875</v>
+        <v>1.7914</v>
       </c>
       <c r="V16" t="n">
         <v>-9.5702</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>-27.3451</v>
+        <v>-25.9633</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.1906</v>
+        <v>-11.9558</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.1543</v>
+        <v>-14.0079</v>
       </c>
       <c r="G17" t="n">
-        <v>10.991</v>
+        <v>-27.3569</v>
       </c>
       <c r="H17" t="n">
-        <v>9.7348</v>
+        <v>-17.2306</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2558</v>
+        <v>-10.1268</v>
       </c>
       <c r="J17" t="n">
-        <v>28.9323</v>
+        <v>0.4476000000000003</v>
       </c>
       <c r="K17" t="n">
-        <v>17.4792</v>
+        <v>-4.959</v>
       </c>
       <c r="L17" t="n">
-        <v>11.4532</v>
+        <v>5.4066</v>
       </c>
       <c r="M17" t="n">
-        <v>-17.9414</v>
+        <v>-27.8047</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.7443</v>
+        <v>-12.2715</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.1971</v>
+        <v>-15.5333</v>
       </c>
       <c r="P17" t="n">
-        <v>-20.8757</v>
+        <v>-8.581999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-43.8388</v>
+        <v>-44.5351</v>
       </c>
       <c r="R17" t="n">
-        <v>22.9636</v>
+        <v>35.9532</v>
       </c>
       <c r="S17" t="n">
-        <v>-13.2824</v>
+        <v>14.6457</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.754</v>
+        <v>9.5085</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.5288</v>
+        <v>5.1373</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.1781</v>
+        <v>-4.6695</v>
       </c>
       <c r="W17" t="n">
-        <v>10.4695</v>
+        <v>22.6229</v>
       </c>
       <c r="X17" t="n">
-        <v>-14.6476</v>
+        <v>-27.2926</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>22.4847</v>
+        <v>54.83900000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>38.9563</v>
+        <v>51.65219999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.4713</v>
+        <v>3.186699999999995</v>
       </c>
       <c r="G18" t="n">
         <v>-4.069600000000001</v>
@@ -1828,7 +1828,7 @@
         <v>-60.1621</v>
       </c>
       <c r="I18" t="n">
-        <v>56.0908</v>
+        <v>56.09080000000001</v>
       </c>
       <c r="J18" t="n">
         <v>323.9639</v>
@@ -1855,16 +1855,16 @@
         <v>-509.1387</v>
       </c>
       <c r="R18" t="n">
-        <v>559.0093999999999</v>
+        <v>559.0094</v>
       </c>
       <c r="S18" t="n">
-        <v>8.360299999999995</v>
+        <v>40.7129</v>
       </c>
       <c r="T18" t="n">
-        <v>9.842000000000006</v>
+        <v>22.5385</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.483999999999998</v>
+        <v>18.1772</v>
       </c>
       <c r="V18" t="n">
         <v>-31.675</v>
